--- a/public/templates/qc-report-template.xlsx
+++ b/public/templates/qc-report-template.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="中查报告" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="尾查报告(AQL)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="尾查报告" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="巡查记录" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +53,12 @@
       <b val="1"/>
       <color rgb="00006100"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -114,7 +120,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,15 +486,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -524,11 +530,7 @@
           <t>验货人</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>生产进度(%)</t>
-        </is>
-      </c>
+      <c r="F3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -541,73 +543,84 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>📏 尺寸检验（抽检5件）</t>
+          <t>📊 生产进度</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>部位</t>
+          <t>当前工序</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>尺码</t>
+          <t>已完成工序</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>标准值(cm)</t>
+          <t>剩余工序</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>实测值(cm)</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>偏差(cm)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
+          <t>交期评估</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
       <c r="B8" s="3" t="n"/>
       <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>□ 可按时交  □ 紧张  □ 无法按时</t>
+        </is>
+      </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-    </row>
     <row r="10">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>📏 尺寸检验（抽检3件）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>部位</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>尺码</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>标准值(cm)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>实测值(cm)</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>偏差(cm)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>判定(合格/不合格)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -657,197 +670,182 @@
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
     </row>
+    <row r="18">
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>👁 外观检验</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>检查项目</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>标准要求</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>实际情况</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>严重度</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>色差</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>无色差 / 4级以上</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>做工(车缝)</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>无跳针断线</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>线头</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>无外露线头(≤0.5cm)</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>拼缝</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>对称平整</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>印花/绣花</t>
+          <t>色差</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>位置准确/颜色对</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
+          <t>无色差 / 4级以上</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>污渍</t>
+          <t>做工(车缝)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>无污渍</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
+          <t>无跳针断线</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>整烫</t>
+          <t>线头</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>平整无皱</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
+          <t>无外露线头(≤0.5cm)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>拼缝</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>对称平整</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>⚙ 功能检验</t>
-        </is>
-      </c>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>印花/Logo</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>位置准确/颜色对/Logo清晰</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>检查项目</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>结果(合格/不合格)</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>绣花/Logo</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>针数均匀/无露底/Logo正确</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>拉链</t>
+          <t>污渍</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>顺滑无卡</t>
+          <t>无污渍</t>
         </is>
       </c>
       <c r="C31" s="3" t="n"/>
@@ -858,12 +856,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>纽扣</t>
+          <t>整烫</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>牢固不松</t>
+          <t>平整无皱</t>
         </is>
       </c>
       <c r="C32" s="3" t="n"/>
@@ -871,99 +869,179 @@
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>魔术贴</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>粘合力正常</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-    </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>⚙ 功能检验</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>检查项目</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>标准</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>结果(合格/不合格)</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>问题描述</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>拉链</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>顺滑无卡、不脱齿</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>弹力</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>回弹良好</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>回弹良好、无变形</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>纽扣/按扣</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>牢固不松、扣合正常</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>网纱</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>无顶破、无破洞</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>拉断线测试</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>缝线牢固、不易拉断</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>✅ 中查结论</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>中查结果:</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>□ 继续生产   □ 需整改后继续   □ 停产整改</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>整改要求:</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>业务意见:</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>跟单签名:</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>业务签名:</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>日期:</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A36:F36"/>
+  <mergeCells count="9">
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A42:F42"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="B38:F39"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B44:F45"/>
+    <mergeCell ref="B46:F46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -975,21 +1053,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>绮陌服饰 · 尾期验货报告（AQL）</t>
+          <t>绮陌服饰 · 尾期验货报告</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1099,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>AQL标准</t>
+          <t>客户验货标准</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1131,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>抽检水平</t>
+          <t>抽检标准</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr"/>
@@ -1065,60 +1143,55 @@
       <c r="B8" s="3" t="n"/>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>□ 正常  □ 加严  □ 放宽</t>
+          <t>按客户要求执行</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>💡 美国打折超市客户建议：AQL 2.5（主要缺陷），抽检比例约 8-10%。2000件抽125件，5000件抽200件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>📋 检验项目</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>检查项</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>合格 ✓</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>不合格 ✗</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>不合格说明</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>尺寸</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>做工</t>
+          <t>尺寸</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -1130,7 +1203,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>外观</t>
+          <t>做工</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -1142,7 +1215,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>颜色</t>
+          <t>外观</t>
         </is>
       </c>
       <c r="B15" s="3" t="n"/>
@@ -1154,7 +1227,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>功能(拉链/纽扣等)</t>
+          <t>颜色</t>
         </is>
       </c>
       <c r="B16" s="3" t="n"/>
@@ -1166,7 +1239,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>包装</t>
+          <t>功能(拉链/纽扣等)</t>
         </is>
       </c>
       <c r="B17" s="3" t="n"/>
@@ -1175,156 +1248,81 @@
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
     </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>包装</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>📈 缺陷统计</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>缺陷等级</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>AQL允收数</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>装箱（配比+产品对应）</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>严重缺陷(Critical)</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr"/>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>危及安全/无法使用</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="n"/>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>✅ 尾查结论</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>主要缺陷(Major)</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr"/>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>影响使用/外观严重</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="n"/>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>尾查结果:</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>□ PASS   □ PENDING(待整改复验)   □ FAIL</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>次要缺陷(Minor)</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr"/>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>轻微外观问题</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr"/>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>✅ 尾查结论</t>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>整改要求:</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>业务意见:</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>□ 同意出货  □ 需整改复验  □ 需与客户沟通  □ 拒绝出货</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>尾查结果:</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>□ PASS   □ PENDING(待整改复验)   □ FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>整改要求:</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>业务意见:</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>□ 同意出货  □ 需整改复验  □ 需与客户沟通  □ 拒绝出货</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>跟单签名:</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>业务签名:</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>日期:</t>
         </is>
@@ -1332,14 +1330,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B28:F29"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="A9:F9"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F24"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1351,15 +1349,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1433,7 +1431,11 @@
           <t>完成进度(%)</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>交期评估</t>
+        </is>
+      </c>
       <c r="F7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1441,7 +1443,11 @@
       <c r="B8" s="3" t="n"/>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>□ 可按时交  □ 紧张  □ 无法按时</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="n"/>
     </row>
     <row r="10">
@@ -1483,7 +1489,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>□ 有  □ 无</t>
+          <t>□ 有正确样衣  □ 无/错误</t>
         </is>
       </c>
       <c r="C12" s="3" t="n"/>
@@ -1558,7 +1564,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>后整理</t>
+          <t>后道包装</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1574,12 +1580,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>现场卫生</t>
+          <t>辅料发放与存储</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>□ 合格  □ 不合格</t>
+          <t>□ 有序清晰  □ 混乱/缺失</t>
         </is>
       </c>
       <c r="C18" s="3" t="n"/>
@@ -1590,44 +1596,52 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>⚠ 问题与跟进</t>
+          <t>🔄 上次问题跟进（中查/尾查/上次巡查的遗留问题）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>问题描述</t>
+          <t>上次发现的问题</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>严重度</t>
+          <t>来源(中查/尾查/巡查)</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>责任方</t>
+          <t>整改要求</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>要求整改日期</t>
+          <t>当前状态</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>跟进状态</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr"/>
+          <t>是否关闭</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
       <c r="B22" s="3" t="n"/>
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>□ 已关闭  □ 未关闭</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="n"/>
     </row>
     <row r="23">
@@ -1635,7 +1649,11 @@
       <c r="B23" s="3" t="n"/>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>□ 已关闭  □ 未关闭</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="n"/>
     </row>
     <row r="24">
@@ -1643,7 +1661,11 @@
       <c r="B24" s="3" t="n"/>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>□ 已关闭  □ 未关闭</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="n"/>
     </row>
     <row r="25">
@@ -1651,7 +1673,11 @@
       <c r="B25" s="3" t="n"/>
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>□ 已关闭  □ 未关闭</t>
+        </is>
+      </c>
       <c r="F25" s="3" t="n"/>
     </row>
     <row r="26">
@@ -1659,34 +1685,114 @@
       <c r="B26" s="3" t="n"/>
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>□ 已关闭  □ 未关闭</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>⚠ 本次新发现问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>问题描述</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>严重度</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>责任方</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>要求整改日期</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>跟进状态</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n"/>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n"/>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n"/>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>备注:</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="37"/>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>跟单签名:</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>日期:</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B36:F37"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B28:F29"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A20:F20"/>
   </mergeCells>

--- a/public/templates/qc-report-template.xlsx
+++ b/public/templates/qc-report-template.xlsx
@@ -89,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -103,11 +103,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -121,6 +149,8 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -504,6 +534,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -540,12 +571,18 @@
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>📊 生产进度</t>
         </is>
       </c>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -583,12 +620,18 @@
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>📏 尺寸检验（抽检3件）</t>
         </is>
       </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -702,12 +745,18 @@
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>👁 外观检验</t>
         </is>
       </c>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -869,12 +918,18 @@
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>⚙ 功能检验</t>
         </is>
       </c>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -980,12 +1035,18 @@
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
           <t>✅ 中查结论</t>
         </is>
       </c>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -1014,6 +1075,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
@@ -1031,6 +1093,8 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
+    <row r="50"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B43:F43"/>
@@ -1053,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1071,6 +1135,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1111,12 +1176,18 @@
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>📊 抽检信息</t>
         </is>
       </c>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1153,16 +1224,22 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>💡 美国打折超市客户建议：AQL 2.5（主要缺陷），抽检比例约 8-10%。2000件抽125件，5000件抽200件。</t>
-        </is>
-      </c>
-    </row>
+          <t>💡 美国打折超市客户建议：AQL 2.5（主要缺陷），抽检比例约 8-10%。2000件抽3-5件，按客户要求或公司标准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>📋 检验项目</t>
         </is>
       </c>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1272,12 +1349,18 @@
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t>✅ 尾查结论</t>
         </is>
       </c>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -1311,6 +1394,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
@@ -1328,6 +1412,9 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A11:F11"/>
@@ -1409,6 +1496,11 @@
           <t>📊 生产情况</t>
         </is>
       </c>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1456,6 +1548,11 @@
           <t>🔍 现场检查</t>
         </is>
       </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1599,6 +1696,11 @@
           <t>🔄 上次问题跟进（中查/尾查/上次巡查的遗留问题）</t>
         </is>
       </c>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1698,6 +1800,11 @@
           <t>⚠ 本次新发现问题</t>
         </is>
       </c>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">

--- a/public/templates/qc-report-template.xlsx
+++ b/public/templates/qc-report-template.xlsx
@@ -624,7 +624,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>📏 尺寸检验（抽检3件）</t>
+          <t>📏 尺寸检验</t>
         </is>
       </c>
       <c r="B10" s="9" t="n"/>
@@ -1117,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1135,7 +1135,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1176,7 +1175,6 @@
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -1222,13 +1220,8 @@
       <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>💡 美国打折超市客户建议：AQL 2.5（主要缺陷），抽检比例约 8-10%。2000件抽3-5件，按客户要求或公司标准。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+      <c r="A9" s="8" t="n"/>
+    </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -1349,7 +1342,6 @@
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
@@ -1394,7 +1386,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
@@ -1412,9 +1403,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A11:F11"/>
